--- a/.claude/skills/mice-estimate/assets/mnc_template.xlsx
+++ b/.claude/skills/mice-estimate/assets/mnc_template.xlsx
@@ -5454,9 +5454,6 @@
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="A114:A115"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId1"/>
-  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
